--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_conc_middelhoog.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_conc_middelhoog.xlsx
@@ -400,22 +400,22 @@
         <v>1.552136229771481</v>
       </c>
       <c r="C2">
-        <v>1.493186813606975</v>
+        <v>1.492356719727288</v>
       </c>
       <c r="D2">
         <v>4.559132871428441</v>
       </c>
       <c r="E2">
-        <v>1.456920224378267</v>
+        <v>1.453366582370714</v>
       </c>
       <c r="F2">
         <v>1.550484622924875</v>
       </c>
       <c r="G2">
-        <v>1.570172298926857</v>
+        <v>1.525480897030672</v>
       </c>
       <c r="H2">
-        <v>1.457347192194636</v>
+        <v>1.453782206960007</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -426,22 +426,22 @@
         <v>1.563193023149681</v>
       </c>
       <c r="C3">
-        <v>1.500165029430641</v>
+        <v>1.488135239415128</v>
       </c>
       <c r="D3">
         <v>3.651525841603912</v>
       </c>
       <c r="E3">
-        <v>1.458610037681003</v>
+        <v>1.455025691607578</v>
       </c>
       <c r="F3">
         <v>1.556893586828959</v>
       </c>
       <c r="G3">
-        <v>1.558931202156377</v>
+        <v>1.509979415128001</v>
       </c>
       <c r="H3">
-        <v>1.458595287136383</v>
+        <v>1.455006096426903</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -452,22 +452,22 @@
         <v>1.526684029639688</v>
       </c>
       <c r="C4">
-        <v>1.549274810175597</v>
+        <v>1.488447142412489</v>
       </c>
       <c r="D4">
         <v>4.19838724095648</v>
       </c>
       <c r="E4">
-        <v>1.451047547992394</v>
+        <v>1.447527665020967</v>
       </c>
       <c r="F4">
         <v>1.527468092681717</v>
       </c>
       <c r="G4">
-        <v>1.572365048458049</v>
+        <v>1.507478430886973</v>
       </c>
       <c r="H4">
-        <v>1.451431135937861</v>
+        <v>1.4478970698214</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -478,22 +478,22 @@
         <v>1.545217619614818</v>
       </c>
       <c r="C5">
-        <v>1.601553576152952</v>
+        <v>1.518626883739414</v>
       </c>
       <c r="D5">
         <v>2.426260736299478</v>
       </c>
       <c r="E5">
-        <v>1.446216490933228</v>
+        <v>1.442563428392502</v>
       </c>
       <c r="F5">
         <v>1.537805340834629</v>
       </c>
       <c r="G5">
-        <v>1.57880164550358</v>
+        <v>1.511869181539962</v>
       </c>
       <c r="H5">
-        <v>1.446166112413757</v>
+        <v>1.442526263593065</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -504,22 +504,22 @@
         <v>1.551005964670671</v>
       </c>
       <c r="C6">
-        <v>1.60245914882812</v>
+        <v>1.530706125062322</v>
       </c>
       <c r="D6">
         <v>0.6342104514815053</v>
       </c>
       <c r="E6">
-        <v>1.448875947771871</v>
+        <v>1.445187114311787</v>
       </c>
       <c r="F6">
         <v>1.543419494542329</v>
       </c>
       <c r="G6">
-        <v>1.548287313870725</v>
+        <v>1.506851313985656</v>
       </c>
       <c r="H6">
-        <v>1.448580771627434</v>
+        <v>1.444906103465592</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -530,22 +530,22 @@
         <v>1.549486314736101</v>
       </c>
       <c r="C7">
-        <v>1.641837099424327</v>
+        <v>1.552962579133622</v>
       </c>
       <c r="D7">
         <v>1.000518488509308</v>
       </c>
       <c r="E7">
-        <v>1.461064592524589</v>
+        <v>1.457382261472365</v>
       </c>
       <c r="F7">
         <v>1.542685382166858</v>
       </c>
       <c r="G7">
-        <v>1.587202116579776</v>
+        <v>1.531291161080332</v>
       </c>
       <c r="H7">
-        <v>1.46083899459511</v>
+        <v>1.45717066678732</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -556,22 +556,22 @@
         <v>1.573590969358645</v>
       </c>
       <c r="C8">
-        <v>1.25963316010294</v>
+        <v>1.418000201339182</v>
       </c>
       <c r="D8">
         <v>1.398601356383272</v>
       </c>
       <c r="E8">
-        <v>1.463279494679763</v>
+        <v>1.460950178653511</v>
       </c>
       <c r="F8">
         <v>1.565222802773999</v>
       </c>
       <c r="G8">
-        <v>1.347264377506428</v>
+        <v>1.45737305922209</v>
       </c>
       <c r="H8">
-        <v>1.463289021859106</v>
+        <v>1.460945855504326</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -582,22 +582,22 @@
         <v>1.563634562990192</v>
       </c>
       <c r="C9">
-        <v>1.549120835106843</v>
+        <v>1.484429531390895</v>
       </c>
       <c r="D9">
         <v>1.032885358940226</v>
       </c>
       <c r="E9">
-        <v>1.455019439359379</v>
+        <v>1.451387656235327</v>
       </c>
       <c r="F9">
         <v>1.557877905496986</v>
       </c>
       <c r="G9">
-        <v>1.524252566768622</v>
+        <v>1.489181574708383</v>
       </c>
       <c r="H9">
-        <v>1.455487230471161</v>
+        <v>1.451868550037982</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -608,22 +608,22 @@
         <v>1.34411727247011</v>
       </c>
       <c r="C10">
-        <v>1.639123914208649</v>
+        <v>1.532786781738554</v>
       </c>
       <c r="D10">
         <v>2.919303411800664</v>
       </c>
       <c r="E10">
-        <v>1.44357601379494</v>
+        <v>1.440095572654453</v>
       </c>
       <c r="F10">
         <v>1.375272804597484</v>
       </c>
       <c r="G10">
-        <v>1.602662455506086</v>
+        <v>1.526806511154333</v>
       </c>
       <c r="H10">
-        <v>1.444906915254569</v>
+        <v>1.441425113818204</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -634,22 +634,22 @@
         <v>1.298091163975459</v>
       </c>
       <c r="C11">
-        <v>1.646314611292481</v>
+        <v>1.5401080602619</v>
       </c>
       <c r="D11">
         <v>2.465559063346526</v>
       </c>
       <c r="E11">
-        <v>1.44699511323945</v>
+        <v>1.443486738685015</v>
       </c>
       <c r="F11">
         <v>1.329380741006684</v>
       </c>
       <c r="G11">
-        <v>1.599602480699534</v>
+        <v>1.523495796495839</v>
       </c>
       <c r="H11">
-        <v>1.447518338027816</v>
+        <v>1.444014140732595</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -660,22 +660,22 @@
         <v>1.073177682413108</v>
       </c>
       <c r="C12">
-        <v>1.6308334743146</v>
+        <v>1.520476970468435</v>
       </c>
       <c r="D12">
         <v>0.9315824148048627</v>
       </c>
       <c r="E12">
-        <v>1.42465114317971</v>
+        <v>1.421227856922761</v>
       </c>
       <c r="F12">
         <v>1.082554188446728</v>
       </c>
       <c r="G12">
-        <v>1.56334331424269</v>
+        <v>1.488518234650031</v>
       </c>
       <c r="H12">
-        <v>1.424266206036189</v>
+        <v>1.420851866011045</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -686,22 +686,22 @@
         <v>1.329072515563819</v>
       </c>
       <c r="C13">
-        <v>1.636853583344017</v>
+        <v>1.528901761663319</v>
       </c>
       <c r="D13">
         <v>2.301587582174859</v>
       </c>
       <c r="E13">
-        <v>1.440235713151947</v>
+        <v>1.436759568958574</v>
       </c>
       <c r="F13">
         <v>1.350229857885921</v>
       </c>
       <c r="G13">
-        <v>1.587080947628143</v>
+        <v>1.511740355344143</v>
       </c>
       <c r="H13">
-        <v>1.440926698548765</v>
+        <v>1.437449491461344</v>
       </c>
     </row>
   </sheetData>

--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_conc_middelhoog.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_conc_middelhoog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Zone</t>
   </si>
@@ -28,7 +28,10 @@
     <t>OV</t>
   </si>
   <si>
-    <t>Auto-FietsOV_Fiets</t>
+    <t>Auto-Fiets</t>
+  </si>
+  <si>
+    <t>OV_Fiets</t>
   </si>
   <si>
     <t>Auto_OV</t>
@@ -391,6 +394,9 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2">
